--- a/public/crawlability-manpowercare-september-2026.xlsx
+++ b/public/crawlability-manpowercare-september-2026.xlsx
@@ -642,7 +642,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>קישורי Cloudflare (ללא טיפול)</t>
+          <t>קישורים ללא צורך בטיפול (Cloudflare, הפניות לדומיין חיצוני)</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">

--- a/public/crawlability-manpowercare-september-2026.xlsx
+++ b/public/crawlability-manpowercare-september-2026.xlsx
@@ -40,7 +40,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -55,11 +55,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F8D7DA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D1ECF1"/>
       </patternFill>
     </fill>
     <fill>
@@ -80,7 +75,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -91,13 +86,10 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -465,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -501,22 +493,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>update.manpowercare.co.il: עותק מלא של האתר, מוגן רק ב-canonical לדומיין הראשי. להגן בסיסמה או להגדיר noindex; אם אינו בשימוש, להסיר.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>לבדיקה</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>לאשר ש-20 העמודים המוגדרים noindex אכן אמורים להישאר מחוץ לאינדקס.</t>
+          <t>update.manpowercare.co.il: עותק מלא של האתר, מוגן רק ב-canonical לדומיין הראשי. להגן בסיסמה או להגדיר X-Robots-Tag: noindex; אם אינו בשימוש, להסיר.</t>
         </is>
       </c>
     </row>
@@ -605,7 +582,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>https://manpowercare.co.il/cdn-cgi/l/email-protection</t>
         </is>
@@ -625,7 +602,7 @@
       <c r="F2" s="2" t="n">
         <v>34</v>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>https://manpowercare.co.il/תנאי-שימוש/
 https://manpowercare.co.il/נגישות/
@@ -651,7 +628,7 @@
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="6" t="inlineStr">
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>נמוכה</t>
         </is>
@@ -728,7 +705,7 @@
           <t>שורת Sitemap</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>https://manpowercare.co.il/sitemap_index.xml</t>
         </is>
@@ -782,7 +759,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>https://manpowercare.co.il/sitemap_index.xml</t>
         </is>
@@ -804,7 +781,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>https://manpowercare.co.il/post-sitemap.xml</t>
         </is>
@@ -826,7 +803,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>https://manpowercare.co.il/page-sitemap.xml</t>
         </is>
@@ -848,7 +825,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>https://manpowercare.co.il/branch-sitemap.xml</t>
         </is>
@@ -870,7 +847,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>https://manpowercare.co.il/category-sitemap.xml</t>
         </is>
@@ -892,7 +869,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>https://manpowercare.co.il/sitemap.xml</t>
         </is>
@@ -914,7 +891,7 @@
           <t>קובץ</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>https://manpowercare.co.il/wp-sitemap.xml</t>
         </is>
@@ -953,7 +930,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>https://manpowercare.co.il/</t>
         </is>
@@ -963,7 +940,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D14" s="5" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>https://manpowercare.co.il/ (0 הפניות)</t>
         </is>
@@ -975,7 +952,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>http://manpowercare.co.il/</t>
         </is>
@@ -985,7 +962,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>https://manpowercare.co.il/ (1 הפניות)</t>
         </is>
@@ -997,7 +974,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>https://www.manpowercare.co.il/</t>
         </is>
@@ -1007,7 +984,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D16" s="5" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>https://manpowercare.co.il/ (1 הפניות)</t>
         </is>
@@ -1019,7 +996,7 @@
           <t>גרסאות דומיין</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>http://www.manpowercare.co.il/</t>
         </is>
@@ -1029,7 +1006,7 @@
           <t>200</t>
         </is>
       </c>
-      <c r="D17" s="5" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>https://manpowercare.co.il/ (2 הפניות)</t>
         </is>
@@ -1082,7 +1059,7 @@
           <t>canonical</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>https://manpowercare.co.il/</t>
         </is>
@@ -1100,7 +1077,7 @@
           <t>Cookie Policy - Manpower Care</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>https://manpowercare.co.il/cookie-policy/</t>
         </is>
@@ -1122,7 +1099,7 @@
           <t>ארכיון צפון - Manpower Care</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>https://manpowercare.co.il/branch_area/צפון/</t>
         </is>
@@ -1144,7 +1121,7 @@
           <t>ארכיון מרכז - Manpower Care</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" s="4" t="inlineStr">
         <is>
           <t>https://manpowercare.co.il/branch_area/מרכז/</t>
         </is>
@@ -1166,7 +1143,7 @@
           <t>נאהלה מלחם - Manpower Care</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>https://manpowercare.co.il/branchmanager/נאהלה-מלחם/</t>
         </is>
@@ -1188,7 +1165,7 @@
           <t>אביה גמזו - Manpower Care</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C25" s="4" t="inlineStr">
         <is>
           <t>https://manpowercare.co.il/branchmanager/אביה-גמזו/</t>
         </is>
@@ -1210,7 +1187,7 @@
           <t>אלכס סבירדצ'יק - Manpower Care</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C26" s="4" t="inlineStr">
         <is>
           <t>https://manpowercare.co.il/branchmanager/אלכס-סבירדציק/</t>
         </is>
@@ -1232,7 +1209,7 @@
           <t>יוליה טולצ'ינסקי - Manpower Care</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>https://manpowercare.co.il/branchmanager/יוליה-טולצינסקי/</t>
         </is>
@@ -1254,7 +1231,7 @@
           <t>אירנה אלנתנוב - Manpower Care</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C28" s="4" t="inlineStr">
         <is>
           <t>https://manpowercare.co.il/branchmanager/אירנה-אלנתנוב/</t>
         </is>
@@ -1276,7 +1253,7 @@
           <t>יוספה אישיצקי - Manpower Care</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C29" s="4" t="inlineStr">
         <is>
           <t>https://manpowercare.co.il/branchmanager/יוספה-אישיצקי/</t>
         </is>
@@ -1298,7 +1275,7 @@
           <t>ריהאם ברהום - Manpower Care</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C30" s="4" t="inlineStr">
         <is>
           <t>https://manpowercare.co.il/branchmanager/ריאהם-ברהום/</t>
         </is>
@@ -1320,7 +1297,7 @@
           <t>רנה דנילוב - Manpower Care</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>https://manpowercare.co.il/branchmanager/רנה-דנילוב/</t>
         </is>
@@ -1342,7 +1319,7 @@
           <t>מרינה וינטר - Manpower Care</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>https://manpowercare.co.il/branchmanager/מרינה-וינטר/</t>
         </is>
@@ -1364,7 +1341,7 @@
           <t>ויסאל מסאלחה - Manpower Care</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C33" s="4" t="inlineStr">
         <is>
           <t>https://manpowercare.co.il/branchmanager/ויסאל-מסאלחה/</t>
         </is>
@@ -1386,7 +1363,7 @@
           <t>ליזה לוין - Manpower Care</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>https://manpowercare.co.il/branchmanager/ליזה-לוין/</t>
         </is>
@@ -1408,7 +1385,7 @@
           <t>סיון זיו - Manpower Care</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>https://manpowercare.co.il/branchmanager/סיון-זיו/</t>
         </is>
@@ -1430,7 +1407,7 @@
           <t>אושרי גוטמן - Manpower Care</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>https://manpowercare.co.il/branchmanager/אושרי-גוטמן/</t>
         </is>
@@ -1452,7 +1429,7 @@
           <t>מרינה חייקין - Manpower Care</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>https://manpowercare.co.il/branchmanager/מרינה-חייקין/</t>
         </is>
@@ -1474,7 +1451,7 @@
           <t>ארכיון מנהלי סניף - Manpower Care</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>https://manpowercare.co.il/branchmanager/</t>
         </is>
@@ -1496,7 +1473,7 @@
           <t>ארכיון מרכז - עמוד 2 מתוך 2 - Manpower Care</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C39" s="4" t="inlineStr">
         <is>
           <t>https://manpowercare.co.il/branch_area/מרכז/page/2/</t>
         </is>
@@ -1518,7 +1495,7 @@
           <t>עדי דב רולנשטיין - Manpower Care</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C40" s="4" t="inlineStr">
         <is>
           <t>https://manpowercare.co.il/branchmanager/עדי-דב-רולנשטיין/</t>
         </is>
@@ -1622,7 +1599,7 @@
           <t>index, follow, max-image-preview:large, max-snippet:-1, max-video-preview:-1</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>https://manpowercare.co.il/</t>
         </is>
@@ -1639,7 +1616,7 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>עותק מלא של האתר, מוגן רק ב-canonical לדומיין הראשי. להגן בסיסמה או להגדיר noindex; אם אינו בשימוש, להסיר.</t>
+          <t>עותק מלא של האתר, מוגן רק ב-canonical לדומיין הראשי. להגן בסיסמה או להגדיר X-Robots-Tag: noindex; אם אינו בשימוש, להסיר.</t>
         </is>
       </c>
       <c r="I2" s="3" t="inlineStr">
